--- a/docs/附录1：软件需求清单模板.xlsx
+++ b/docs/附录1：软件需求清单模板.xlsx
@@ -1,68 +1,519 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xiaoye\Documents\研究生\软测\实践作业-文档模板2025\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="软件需求清单" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>功能模块名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>子模块名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>功能描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据上传与格式识别</t>
+  </si>
+  <si>
+    <t>文件上传</t>
+  </si>
+  <si>
+    <t>用户可选择并上传 CSV 或 JSON 图数据文件，前端以 multipart/form-data 提交给后端。</t>
+  </si>
+  <si>
+    <t>文件格式校验</t>
+  </si>
+  <si>
+    <t>系统校验文件扩展名和文件参数，拒绝缺失文件或非 CSV、JSON 文件，并返回提示信息。</t>
+  </si>
+  <si>
+    <t>数据模式识别</t>
+  </si>
+  <si>
+    <t>系统根据 JSON 的 mode 字段或 CSV 的字段结构识别 timestamp 或 snapshot 数据模式。</t>
+  </si>
+  <si>
+    <t>数据读取与建图</t>
+  </si>
+  <si>
+    <t>CSV 数据读取</t>
+  </si>
+  <si>
+    <t>读取 CSV 中的节点、边和时间信息，转换为统一的图数据结构。</t>
+  </si>
+  <si>
+    <t>JSON 数据读取</t>
+  </si>
+  <si>
+    <t>读取 timestamp 或 snapshot 格式的 JSON 数据，保留节点、边和时间信息。</t>
+  </si>
+  <si>
+    <t>时间戳图构建</t>
+  </si>
+  <si>
+    <t>将时间戳边数据构建为有向多重图，支持同一节点对在多个时间点产生边。</t>
+  </si>
+  <si>
+    <t>快照图构建</t>
+  </si>
+  <si>
+    <t>按快照时间分别构建有向图，保留每个快照的节点和边集合。</t>
+  </si>
+  <si>
+    <t>图指标计算与序列化</t>
+  </si>
+  <si>
+    <t>图数据序列化</t>
+  </si>
+  <si>
+    <t>将 NetworkX 图转换为前端可使用的 nodes 和 links 数据结构。</t>
+  </si>
+  <si>
+    <t>节点指标计算</t>
+  </si>
+  <si>
+    <t>计算节点度数、PageRank 值和社区分组，用于图分析与节点详情展示。</t>
+  </si>
+  <si>
+    <t>图可视化与交互</t>
+  </si>
+  <si>
+    <t>时间戳图展示</t>
+  </si>
+  <si>
+    <t>加载并展示时间戳图，用户可通过时间范围筛选当前显示的边和节点。</t>
+  </si>
+  <si>
+    <t>快照图展示</t>
+  </si>
+  <si>
+    <t>以多个子图展示不同时间点的快照网络。</t>
+  </si>
+  <si>
+    <t>节点详情</t>
+  </si>
+  <si>
+    <t>用户选择节点后，可查看节点的度数、PageRank 值和所属社区。</t>
+  </si>
+  <si>
+    <t>最短路径</t>
+  </si>
+  <si>
+    <t>有向最短路径计算</t>
+  </si>
+  <si>
+    <t>根据当前展示的连线和起止节点计算有向最短路径；无路径或节点不存在时返回明确提示。</t>
+  </si>
+  <si>
+    <t>异常处理</t>
+  </si>
+  <si>
+    <t>输入与处理异常反馈</t>
+  </si>
+  <si>
+    <t>对缺少参数、数据字段错误、JSON 解析错误和不存在路径等情况返回可识别的错误信息。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -70,27 +521,545 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -139,74 +1108,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -262,7 +1171,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -271,13 +1180,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -311,17 +1220,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -377,21 +1275,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="2" width="20.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="69.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.77734375" customWidth="1"/>
+    <col min="1" max="1" width="22" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="68" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,29 +1304,204 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" ht="26.4" customHeight="1" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="26.4" customHeight="1" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" ht="26.4" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" ht="26.4" customHeight="1" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" spans="1:4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>